--- a/Inventory/Assets/Excel/Equipment/EquipmentData.xlsx
+++ b/Inventory/Assets/Excel/Equipment/EquipmentData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\00 GitHub\Game_Team\Assets\Excel\Equipment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\00 GitHub\Game_Team\Inventory\Assets\Excel\Equipment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4A4E1A2-F6F7-4B43-9A57-D7A9441F3FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDAD008-E934-4E38-909A-5BC1054361F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>id</t>
   </si>
@@ -75,6 +75,10 @@
   </si>
   <si>
     <t>attackSpeed</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>condition</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -457,14 +461,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J99"/>
+  <dimension ref="A1:K99"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
-    <col min="2" max="10" width="15.625" customWidth="1"/>
+    <col min="2" max="11" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -495,8 +499,11 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -527,8 +534,11 @@
       <c r="J2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -559,8 +569,11 @@
       <c r="J3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -591,8 +604,11 @@
       <c r="J4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -623,13 +639,16 @@
       <c r="J5">
         <v>50</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -641,7 +660,7 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -655,8 +674,11 @@
       <c r="J6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
@@ -673,10 +695,10 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -687,16 +709,19 @@
       <c r="J7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -719,8 +744,11 @@
       <c r="J8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -731,13 +759,13 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -751,13 +779,16 @@
       <c r="J9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -766,7 +797,7 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -775,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -783,8 +814,11 @@
       <c r="J10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
@@ -792,7 +826,7 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -813,10 +847,13 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+      <c r="K11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
@@ -833,7 +870,7 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -847,8 +884,11 @@
       <c r="J12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
@@ -862,7 +902,7 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -871,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -879,8 +919,11 @@
       <c r="J13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
@@ -911,8 +954,11 @@
       <c r="J14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
@@ -920,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -943,8 +989,11 @@
       <c r="J15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
@@ -970,13 +1019,16 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+      <c r="K16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
@@ -987,7 +1039,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -996,7 +1048,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -1007,13 +1059,16 @@
       <c r="J17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1022,7 +1077,7 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1039,8 +1094,11 @@
       <c r="J18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1071,8 +1129,11 @@
       <c r="J19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1080,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1098,18 +1159,21 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1127,16 +1191,19 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+      <c r="K21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1156,40 +1223,43 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="30" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="31" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="32" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="29" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="30" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="31" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="32" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="33" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="34" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="35" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
